--- a/AAII_Financials/Quarterly/BAESY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BAESY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="578" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="618" uniqueCount="92">
   <si>
     <t>BAESY</t>
   </si>
@@ -656,85 +656,87 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:U102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="21" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="23" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="R7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S7" s="2" t="s">
         <v>3</v>
       </c>
@@ -744,8 +746,14 @@
       <c r="U7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="W7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -803,8 +811,14 @@
       <c r="U8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -862,8 +876,14 @@
       <c r="U9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -921,8 +941,14 @@
       <c r="U10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -944,8 +970,10 @@
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V11" s="3"/>
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1003,8 +1031,14 @@
       <c r="U12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1062,8 +1096,14 @@
       <c r="U13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1106,23 +1146,29 @@
       <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
-      <c r="R14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S14" s="3">
         <v>0</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U14" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1165,23 +1211,29 @@
       <c r="P15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
-      <c r="R15" s="3">
-        <v>0</v>
+      <c r="Q15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S15" s="3">
         <v>0</v>
       </c>
-      <c r="T15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U15" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="T15" s="3">
+        <v>0</v>
+      </c>
+      <c r="U15" s="3">
+        <v>0</v>
+      </c>
+      <c r="V15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1200,8 +1252,10 @@
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
-    </row>
-    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V16" s="3"/>
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1259,8 +1313,14 @@
       <c r="U17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1318,8 +1378,14 @@
       <c r="U18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1341,8 +1407,10 @@
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
-    </row>
-    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V19" s="3"/>
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1400,8 +1468,14 @@
       <c r="U20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1459,8 +1533,14 @@
       <c r="U21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1503,23 +1583,29 @@
       <c r="P22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
-      </c>
-      <c r="R22" s="3">
-        <v>0</v>
+      <c r="Q22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S22" s="3">
         <v>0</v>
       </c>
-      <c r="T22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U22" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="T22" s="3">
+        <v>0</v>
+      </c>
+      <c r="U22" s="3">
+        <v>0</v>
+      </c>
+      <c r="V22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1577,8 +1663,14 @@
       <c r="U23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1636,8 +1728,14 @@
       <c r="U24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1695,8 +1793,14 @@
       <c r="U25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1754,8 +1858,14 @@
       <c r="U26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1813,8 +1923,14 @@
       <c r="U27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1872,8 +1988,14 @@
       <c r="U28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1916,23 +2038,29 @@
       <c r="P29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q29" s="3">
-        <v>0</v>
-      </c>
-      <c r="R29" s="3">
-        <v>0</v>
+      <c r="Q29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S29" s="3">
         <v>0</v>
       </c>
-      <c r="T29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U29" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+      <c r="V29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W29" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1990,8 +2118,14 @@
       <c r="U30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2049,8 +2183,14 @@
       <c r="U31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2108,8 +2248,14 @@
       <c r="U32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -2167,8 +2313,14 @@
       <c r="U33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2226,8 +2378,14 @@
       <c r="U34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -2285,61 +2443,67 @@
       <c r="U35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="R38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2349,8 +2513,14 @@
       <c r="U38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="W38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2372,8 +2542,10 @@
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
-    </row>
-    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V39" s="3"/>
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2395,56 +2567,58 @@
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
-    </row>
-    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V40" s="3"/>
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>5572500</v>
+      </c>
+      <c r="E41" s="3">
+        <v>5546000</v>
+      </c>
+      <c r="F41" s="3">
         <v>4627200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>4621300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>2949700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>2781700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>4229000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>4527500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>3577800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>3575500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>5180400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>4963000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>4071600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>3963800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>3743600</v>
       </c>
-      <c r="Q41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2454,56 +2628,62 @@
       <c r="U41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
         <v>41700</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>41700</v>
       </c>
-      <c r="F42" s="3">
-        <v>0</v>
-      </c>
-      <c r="G42" s="3">
-        <v>0</v>
-      </c>
       <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
         <v>61300</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>65700</v>
       </c>
-      <c r="J42" s="3">
-        <v>0</v>
-      </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
       <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3">
         <v>54800</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>52500</v>
       </c>
-      <c r="N42" s="3">
-        <v>0</v>
-      </c>
-      <c r="O42" s="3">
-        <v>0</v>
-      </c>
       <c r="P42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+      <c r="R42" s="3">
         <v>27700</v>
       </c>
-      <c r="Q42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2513,56 +2693,62 @@
       <c r="U42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>10701900</v>
+      </c>
+      <c r="E43" s="3">
+        <v>10650900</v>
+      </c>
+      <c r="F43" s="3">
         <v>8300100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>8289600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>10060300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>9487200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>7241100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>7752300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>9080300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>9074500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>6840100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>6553100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>8248700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>8030200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>6929300</v>
       </c>
-      <c r="Q43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2572,56 +2758,62 @@
       <c r="U43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2037900</v>
+      </c>
+      <c r="E44" s="3">
+        <v>2028200</v>
+      </c>
+      <c r="F44" s="3">
         <v>1862700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>1860400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>1878300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>1771300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>1657500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>1774600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>1712400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>1711300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>1472500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>1410700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>1330500</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>1295300</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>1176000</v>
       </c>
-      <c r="Q44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2631,115 +2823,127 @@
       <c r="U44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>205700</v>
+      </c>
+      <c r="E45" s="3">
+        <v>204700</v>
+      </c>
+      <c r="F45" s="3">
         <v>273200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>272900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>398700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>376000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>266700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>285500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>200900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>200800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>259800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>248900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>258000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>251100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>322900</v>
       </c>
-      <c r="Q45" s="3">
-        <v>0</v>
-      </c>
-      <c r="R45" s="3">
-        <v>0</v>
-      </c>
       <c r="S45" s="3">
         <v>0</v>
       </c>
-      <c r="T45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U45" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="T45" s="3">
+        <v>0</v>
+      </c>
+      <c r="U45" s="3">
+        <v>0</v>
+      </c>
+      <c r="V45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>18518000</v>
+      </c>
+      <c r="E46" s="3">
+        <v>18429800</v>
+      </c>
+      <c r="F46" s="3">
         <v>16348600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>16327900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>15287000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>14416200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>14713900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>15752600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>14571500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>14562100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>14995900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>14366800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>13908800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>13540400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>12812800</v>
       </c>
-      <c r="Q46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2749,56 +2953,62 @@
       <c r="U46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1066700</v>
+      </c>
+      <c r="E47" s="3">
+        <v>1061700</v>
+      </c>
+      <c r="F47" s="3">
         <v>1214000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>1212500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>983700</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>927700</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>1272000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>1361700</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>997100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>996500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>1294100</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>1239800</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>1023000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>995900</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>1244700</v>
       </c>
-      <c r="Q47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2808,56 +3018,62 @@
       <c r="U47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>9202600</v>
+      </c>
+      <c r="E48" s="3">
+        <v>9158800</v>
+      </c>
+      <c r="F48" s="3">
         <v>9149400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>9137800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>8819000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>8316600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>8260200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>8843300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>7931600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>7926400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>6300000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>6035700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>5899000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>5742800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>5614800</v>
       </c>
-      <c r="Q48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2867,56 +3083,62 @@
       <c r="U48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>20367500</v>
+      </c>
+      <c r="E49" s="3">
+        <v>20270600</v>
+      </c>
+      <c r="F49" s="3">
         <v>20417200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>20391400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>20820700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>19634600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>20284900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>21716900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>20277500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>20264500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>15343700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>14699900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>15417300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>15008900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>15174400</v>
       </c>
-      <c r="Q49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2926,8 +3148,14 @@
       <c r="U49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2985,8 +3213,14 @@
       <c r="U50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3044,56 +3278,62 @@
       <c r="U51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>3455000</v>
+      </c>
+      <c r="E52" s="3">
+        <v>3438500</v>
+      </c>
+      <c r="F52" s="3">
         <v>3071300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>3067500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>2889400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>2724800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>2594000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>2777100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>2784100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>2782300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>2022700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>1937900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>2685200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>2614100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>2541100</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3103,8 +3343,14 @@
       <c r="U52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3162,56 +3408,62 @@
       <c r="U53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>52929500</v>
+      </c>
+      <c r="E54" s="3">
+        <v>52677600</v>
+      </c>
+      <c r="F54" s="3">
         <v>50712000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>50647900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>49323200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>46513500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>47750900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>51121800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>47035800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>47005500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>40841700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>39128200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>39347600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>38305400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>37908300</v>
       </c>
-      <c r="Q54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3221,8 +3473,14 @@
       <c r="U54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3244,8 +3502,10 @@
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
-    </row>
-    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V55" s="3"/>
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3267,56 +3527,58 @@
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
-    </row>
-    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V56" s="3"/>
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>9038100</v>
+      </c>
+      <c r="E57" s="3">
+        <v>8995100</v>
+      </c>
+      <c r="F57" s="3">
         <v>4506100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>4500400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>8361400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>7885100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>3857200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>4129500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>7059500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>7055000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>3057000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>2928800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>6296800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>6130000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>2289300</v>
       </c>
-      <c r="Q57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3326,56 +3588,62 @@
       <c r="U57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1186100</v>
+      </c>
+      <c r="E58" s="3">
+        <v>1180500</v>
+      </c>
+      <c r="F58" s="3">
         <v>508700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>508100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>1115200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>1051700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>1153000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>1234400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>1223300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>1222600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>1193500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>1143400</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>316400</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>308000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>449400</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3385,56 +3653,62 @@
       <c r="U58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>7916900</v>
+      </c>
+      <c r="E59" s="3">
+        <v>7879300</v>
+      </c>
+      <c r="F59" s="3">
         <v>7554500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>7545000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>6462500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>6094400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>6737900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>7213500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>5862700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>5859000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>6229900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>5968600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>6407300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>6237600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>5758200</v>
       </c>
-      <c r="Q59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3444,56 +3718,62 @@
       <c r="U59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>18141200</v>
+      </c>
+      <c r="E60" s="3">
+        <v>18054800</v>
+      </c>
+      <c r="F60" s="3">
         <v>16558500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>16537600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>15939200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>15031200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>15451300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>16542000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>14145600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>14136500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>13938700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>13353900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>13020500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>12675700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>11863400</v>
       </c>
-      <c r="Q60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3503,56 +3783,62 @@
       <c r="U60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>10957900</v>
+      </c>
+      <c r="E61" s="3">
+        <v>10905800</v>
+      </c>
+      <c r="F61" s="3">
         <v>11818300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>11803400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>11801600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>11129300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>11761800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>12592100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>12445800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>12437800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>7339400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>7031500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>8083500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>7869400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>7951100</v>
       </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
-      <c r="R61" s="3">
-        <v>0</v>
-      </c>
       <c r="S61" s="3">
         <v>0</v>
       </c>
@@ -3562,56 +3848,62 @@
       <c r="U61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V61" s="3">
+        <v>0</v>
+      </c>
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>3458900</v>
+      </c>
+      <c r="E62" s="3">
+        <v>3442500</v>
+      </c>
+      <c r="F62" s="3">
         <v>1481800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>1480000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>3484000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>3285600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>1382100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>1479700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>2949700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>2947800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>1212600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>1161700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>2591100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>2522500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>1216900</v>
       </c>
-      <c r="Q62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3621,8 +3913,14 @@
       <c r="U62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3680,8 +3978,14 @@
       <c r="U63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3739,8 +4043,14 @@
       <c r="U64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3798,56 +4108,62 @@
       <c r="U65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>36282300</v>
+      </c>
+      <c r="E66" s="3">
+        <v>36109600</v>
+      </c>
+      <c r="F66" s="3">
         <v>34646000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>34602300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>34236200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>32285900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>33007000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>35337100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>32551500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>32530500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>27183200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>26042800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>25596300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>24918300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>24172500</v>
       </c>
-      <c r="Q66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3857,8 +4173,14 @@
       <c r="U66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3880,8 +4202,10 @@
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
-    </row>
-    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V67" s="3"/>
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3939,8 +4263,14 @@
       <c r="U68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3998,8 +4328,14 @@
       <c r="U69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4051,14 +4387,20 @@
       <c r="S70" s="3">
         <v>0</v>
       </c>
-      <c r="T70" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U70" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="T70" s="3">
+        <v>0</v>
+      </c>
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+      <c r="V70" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W70" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4116,56 +4458,62 @@
       <c r="U71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>6700300</v>
+      </c>
+      <c r="E72" s="3">
+        <v>6668400</v>
+      </c>
+      <c r="F72" s="3">
         <v>6424000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>6415800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>5289800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>4988400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>5055300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>5412100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>4334800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>4332000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>3851800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>3690200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>3677700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>3580300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>3773700</v>
       </c>
-      <c r="Q72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4175,8 +4523,14 @@
       <c r="U72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4234,8 +4588,14 @@
       <c r="U73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4293,8 +4653,14 @@
       <c r="U74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4352,56 +4718,62 @@
       <c r="U75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>16419000</v>
+      </c>
+      <c r="E76" s="3">
+        <v>16340800</v>
+      </c>
+      <c r="F76" s="3">
         <v>15860000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>15840000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>14848600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>14002800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>14542400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>15569000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>14229000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>14219900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>13449600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>12885300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>13493300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>13135900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>13512900</v>
       </c>
-      <c r="Q76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4411,8 +4783,14 @@
       <c r="U76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4470,61 +4848,67 @@
       <c r="U77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="R80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S80" s="2" t="s">
         <v>3</v>
       </c>
@@ -4534,8 +4918,14 @@
       <c r="U80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="W80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -4593,8 +4983,14 @@
       <c r="U81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4616,67 +5012,75 @@
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
-    </row>
-    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V82" s="3"/>
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>261700</v>
+      </c>
+      <c r="E83" s="3">
+        <v>246800</v>
+      </c>
+      <c r="F83" s="3">
         <v>190900</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>204400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>226200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>226100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>149000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>142800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>209700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>204100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>144000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>133200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>188300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>203700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>148300</v>
       </c>
-      <c r="Q83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S83" s="3">
-        <v>0</v>
+      <c r="S83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U83" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="U83" s="3">
+        <v>0</v>
+      </c>
+      <c r="V83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4734,8 +5138,14 @@
       <c r="U84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4793,8 +5203,14 @@
       <c r="U85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4852,8 +5268,14 @@
       <c r="U86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4911,8 +5333,14 @@
       <c r="U87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4970,67 +5398,79 @@
       <c r="U88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1488000</v>
+      </c>
+      <c r="E89" s="3">
+        <v>1480900</v>
+      </c>
+      <c r="F89" s="3">
         <v>2259800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>2256900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>50700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>47800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>1983000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>2123000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>478300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>478000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>1449500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>1388700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>942900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>918000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>1413300</v>
       </c>
-      <c r="Q89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S89" s="3">
-        <v>0</v>
+      <c r="S89" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U89" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="U89" s="3">
+        <v>0</v>
+      </c>
+      <c r="V89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5052,67 +5492,75 @@
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
-    </row>
-    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V90" s="3"/>
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-238200</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-237000</v>
+      </c>
+      <c r="F91" s="3">
         <v>-366100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-365600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-257600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-242900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-378700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-405400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-243300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-243100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-314600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-301400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-211000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-205400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-212100</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
-      <c r="R91" s="3">
-        <v>0</v>
-      </c>
       <c r="S91" s="3">
         <v>0</v>
       </c>
-      <c r="T91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U91" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="T91" s="3">
+        <v>0</v>
+      </c>
+      <c r="U91" s="3">
+        <v>0</v>
+      </c>
+      <c r="V91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5170,8 +5618,14 @@
       <c r="U92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5229,67 +5683,79 @@
       <c r="U93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-129400</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-128700</v>
+      </c>
+      <c r="F94" s="3">
         <v>-314900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-314500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-50000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-47200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-438200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-469100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-2887100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-2885300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-262400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-251400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-82000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-79800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-97000</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S94" s="3">
-        <v>0</v>
+      <c r="S94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U94" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="U94" s="3">
+        <v>0</v>
+      </c>
+      <c r="V94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5311,56 +5777,58 @@
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
-    </row>
-    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V95" s="3"/>
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>455100</v>
+      </c>
+      <c r="E96" s="3">
+        <v>452900</v>
+      </c>
+      <c r="F96" s="3">
         <v>272500</v>
       </c>
-      <c r="E96" s="3">
+      <c r="G96" s="3">
         <v>272200</v>
       </c>
-      <c r="F96" s="3">
+      <c r="H96" s="3">
         <v>426100</v>
       </c>
-      <c r="G96" s="3">
+      <c r="I96" s="3">
         <v>401800</v>
       </c>
-      <c r="H96" s="3">
+      <c r="J96" s="3">
         <v>234700</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>251300</v>
       </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3">
         <v>355100</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>354900</v>
       </c>
-      <c r="L96" s="3">
+      <c r="N96" s="3">
         <v>222300</v>
       </c>
-      <c r="M96" s="3">
+      <c r="O96" s="3">
         <v>212900</v>
       </c>
-      <c r="N96" s="3">
+      <c r="P96" s="3">
         <v>322800</v>
       </c>
-      <c r="O96" s="3">
+      <c r="Q96" s="3">
         <v>314200</v>
       </c>
-      <c r="P96" s="3">
+      <c r="R96" s="3">
         <v>194000</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
-      <c r="R96" s="3">
-        <v>0</v>
-      </c>
       <c r="S96" s="3">
         <v>0</v>
       </c>
@@ -5370,8 +5838,14 @@
       <c r="U96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5429,8 +5903,14 @@
       <c r="U97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5488,8 +5968,14 @@
       <c r="U98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5547,181 +6033,205 @@
       <c r="U99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-869000</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-864900</v>
+      </c>
+      <c r="F100" s="3">
         <v>-1086100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-1084800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-794600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-749400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-1181800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-1265200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>1632200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>1631100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-629200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-602800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-762500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-742300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-653700</v>
       </c>
-      <c r="Q100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S100" s="3">
-        <v>0</v>
+      <c r="S100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U100" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="U100" s="3">
+        <v>0</v>
+      </c>
+      <c r="V100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-45200</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-42600</v>
+      </c>
+      <c r="F101" s="3">
         <v>-20700</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-22100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>-4400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-4400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>-8300</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-7900</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>-36900</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-35900</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>30700</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>28400</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>33400</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>36100</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>5400</v>
       </c>
-      <c r="Q101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S101" s="3">
-        <v>0</v>
+      <c r="S101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U101" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="U101" s="3">
+        <v>0</v>
+      </c>
+      <c r="V101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>503500</v>
+      </c>
+      <c r="E102" s="3">
+        <v>501100</v>
+      </c>
+      <c r="F102" s="3">
         <v>864700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>863600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-839200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-791400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>342400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>366600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-781000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-780500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>549600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>526600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>61600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>60000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>693400</v>
       </c>
-      <c r="Q102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S102" s="3">
-        <v>0</v>
+      <c r="S102" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U102" s="3" t="s">
+      <c r="U102" s="3">
+        <v>0</v>
+      </c>
+      <c r="V102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
